--- a/basedatos_partidas/salida/descompuestos/CT-04-01-080.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-080.xlsx
@@ -539,10 +539,10 @@
         <v>0.14</v>
       </c>
       <c r="G10" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>17.5</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>21.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="12">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>70.62</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -958,10 +958,10 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>104.97</v>
+        <v>101.59</v>
       </c>
       <c r="H30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="31">
@@ -977,7 +977,7 @@
       </c>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="5" t="n">
-        <v>106.02</v>
+        <v>102.61</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-04-01-080.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-080.xlsx
@@ -591,10 +591,10 @@
         <v>0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="13">
@@ -617,10 +617,10 @@
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>16.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="14">
@@ -643,10 +643,10 @@
         <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>6.72</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="15">
@@ -669,10 +669,10 @@
         <v>0.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="16">
@@ -695,10 +695,10 @@
         <v>0.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>0.54</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="17">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>67.23999999999999</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="18">
@@ -958,10 +958,10 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>101.59</v>
+        <v>137.95</v>
       </c>
       <c r="H30" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="31">
@@ -977,7 +977,7 @@
       </c>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="5" t="n">
-        <v>102.61</v>
+        <v>139.33</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-04-01-080.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-080.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 04 Fundaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Bases y zapatas</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
